--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -170,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,12 +180,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -236,17 +230,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,22 +46,10 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1124 Плевен Христо Ботев</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1918 O5 Търговище</t>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В8986ВР</t>
@@ -74,48 +59,6 @@
   </si>
   <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>06:49:00</t>
-  </si>
-  <si>
-    <t>06:52:00</t>
-  </si>
-  <si>
-    <t>10:31:00</t>
-  </si>
-  <si>
-    <t>08:45:00</t>
-  </si>
-  <si>
-    <t>14:03:00</t>
-  </si>
-  <si>
-    <t>3232525710 3232525710</t>
-  </si>
-  <si>
-    <t>3232516778 3232516778</t>
-  </si>
-  <si>
-    <t>3232516779 3232516779</t>
-  </si>
-  <si>
-    <t>3232529453 3232529453</t>
-  </si>
-  <si>
-    <t>3232547018 3232547018</t>
-  </si>
-  <si>
-    <t>3232548246 3232548246</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -535,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -544,17 +487,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,371 +528,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>32.78</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H2">
+        <v>22.95</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="J2">
+        <v>23.27</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>13.12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2">
-        <v>0.76</v>
-      </c>
-      <c r="I2" s="1">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="J2">
-        <v>0.77</v>
-      </c>
-      <c r="K2" s="1">
-        <v>10.1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
+      <c r="B7" s="7">
+        <v>32.78</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.7000999999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>22.95</v>
+      </c>
+      <c r="F7" s="7">
+        <v>23.27</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>16.56</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>29.26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>0.76</v>
-      </c>
-      <c r="I4" s="1">
-        <v>22.24</v>
-      </c>
-      <c r="J4">
-        <v>0.77</v>
-      </c>
-      <c r="K4" s="1">
-        <v>22.53</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>10.35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5">
-        <v>0.76</v>
-      </c>
-      <c r="I5" s="1">
-        <v>7.87</v>
-      </c>
-      <c r="J5">
-        <v>0.77</v>
-      </c>
-      <c r="K5" s="1">
-        <v>7.97</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>22.7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6">
-        <v>0.76</v>
-      </c>
-      <c r="I6" s="1">
-        <v>17.25</v>
-      </c>
-      <c r="J6">
-        <v>0.77</v>
-      </c>
-      <c r="K6" s="1">
-        <v>17.48</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>30.23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7">
-        <v>0.76</v>
-      </c>
-      <c r="I7" s="1">
-        <v>22.97</v>
-      </c>
-      <c r="J7">
-        <v>0.77</v>
-      </c>
-      <c r="K7" s="1">
-        <v>23.28</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="7">
-        <v>105.66</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.76</v>
-      </c>
-      <c r="E12" s="7">
-        <v>80.3</v>
-      </c>
-      <c r="F12" s="7">
-        <v>81.36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="7">
-        <v>16.56</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B8" s="10">
+        <v>32.78</v>
+      </c>
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D13" s="8">
-        <v>1.5399</v>
-      </c>
-      <c r="E13" s="7">
-        <v>25.5</v>
-      </c>
-      <c r="F13" s="7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="10">
-        <v>122.22</v>
-      </c>
-      <c r="C14" s="10">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>105.8</v>
-      </c>
-      <c r="F14" s="10">
-        <v>107.36</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>22.95</v>
+      </c>
+      <c r="F8" s="10">
+        <v>23.27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>15:36</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -478,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,10 +500,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -528,22 +539,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46183</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>32.78</v>
@@ -560,13 +577,19 @@
       <c r="J2">
         <v>23.27</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
+      <c r="M2">
+        <v>140669</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -574,18 +597,18 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>7</v>
@@ -594,9 +617,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>32.78</v>
@@ -614,9 +637,9 @@
         <v>23.27</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>32.78</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
@@ -67,7 +61,7 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>15:36</t>
+    <t>2026-06-25 09:41:14</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -487,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,12 +494,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,57 +531,45 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>29.33</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>19.06</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>19.36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="F2">
-        <v>32.78</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="H2">
-        <v>22.95</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="J2">
-        <v>23.27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>140669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -597,18 +577,18 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:11">
       <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>7</v>
@@ -617,42 +597,42 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="7">
-        <v>32.78</v>
+        <v>29.33</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="8">
-        <v>0.7000999999999999</v>
+        <v>0.6498</v>
       </c>
       <c r="E7" s="7">
-        <v>22.95</v>
+        <v>19.06</v>
       </c>
       <c r="F7" s="7">
-        <v>23.27</v>
+        <v>19.36</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:11">
       <c r="A8" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" s="10">
-        <v>32.78</v>
+        <v>29.33</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="10">
-        <v>22.95</v>
+        <v>19.06</v>
       </c>
       <c r="F8" s="10">
-        <v>23.27</v>
+        <v>19.36</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,16 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1909 О5, Хасково</t>
   </si>
   <si>
     <t>В8986ВР</t>
@@ -61,7 +73,34 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-25 09:41:14</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:41:00</t>
+  </si>
+  <si>
+    <t>08:10:00</t>
+  </si>
+  <si>
+    <t>08:11:00</t>
+  </si>
+  <si>
+    <t>14:16:00</t>
+  </si>
+  <si>
+    <t>3233835178 3233835178</t>
+  </si>
+  <si>
+    <t>3234037074 3234037074</t>
+  </si>
+  <si>
+    <t>3234037075 3234037075</t>
+  </si>
+  <si>
+    <t>3234060252 3234060252</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -481,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -490,14 +529,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,113 +573,283 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46198</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>29.33</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
         <v>0.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>19.06</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>19.36</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>12.56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>0.65</v>
+      </c>
+      <c r="I3" s="1">
+        <v>8.16</v>
+      </c>
+      <c r="J3">
+        <v>0.66</v>
+      </c>
+      <c r="K3" s="1">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>12.09</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>1.47</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17.77</v>
+      </c>
+      <c r="J4">
+        <v>1.5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>18.13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="4" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="5" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="F5">
+        <v>31.39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>0.65</v>
+      </c>
+      <c r="I5" s="1">
+        <v>20.4</v>
+      </c>
+      <c r="J5">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>20.72</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7">
+        <v>73.28</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.6498</v>
+      </c>
+      <c r="E10" s="7">
+        <v>47.62</v>
+      </c>
+      <c r="F10" s="7">
+        <v>48.37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="7">
-        <v>29.33</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B11" s="7">
+        <v>12.09</v>
+      </c>
+      <c r="C11" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="8">
-        <v>0.6498</v>
-      </c>
-      <c r="E7" s="7">
-        <v>19.06</v>
-      </c>
-      <c r="F7" s="7">
-        <v>19.36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="10">
-        <v>29.33</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>19.06</v>
-      </c>
-      <c r="F8" s="10">
-        <v>19.36</v>
+      <c r="D11" s="8">
+        <v>1.4698</v>
+      </c>
+      <c r="E11" s="7">
+        <v>17.77</v>
+      </c>
+      <c r="F11" s="7">
+        <v>18.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="10">
+        <v>85.37</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>65.39</v>
+      </c>
+      <c r="F12" s="10">
+        <v>66.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1909 О5, Хасково</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Хасково</t>
   </si>
   <si>
     <t>В8986ВР</t>
@@ -76,31 +76,13 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:41:00</t>
-  </si>
-  <si>
-    <t>08:10:00</t>
-  </si>
-  <si>
-    <t>08:11:00</t>
-  </si>
-  <si>
-    <t>14:16:00</t>
-  </si>
-  <si>
-    <t>3233835178 3233835178</t>
-  </si>
-  <si>
-    <t>3234037074 3234037074</t>
-  </si>
-  <si>
-    <t>3234037075 3234037075</t>
-  </si>
-  <si>
-    <t>3234060252 3234060252</t>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>14:17</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -520,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -529,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,16 +560,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46198</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -602,32 +580,29 @@
       <c r="F2">
         <v>29.33</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>19.06</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>19.36</v>
+      </c>
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>0.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>19.06</v>
-      </c>
-      <c r="J2">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>19.36</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
+      <c r="L2">
+        <v>420594</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>145496</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46202</v>
       </c>
@@ -646,32 +621,29 @@
       <c r="F3">
         <v>12.56</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
+      <c r="G3" s="1">
+        <v>0.65</v>
       </c>
       <c r="H3">
-        <v>0.65</v>
+        <v>8.16</v>
       </c>
       <c r="I3" s="1">
-        <v>8.16</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
         <v>8.289999999999999</v>
       </c>
-      <c r="L3" t="s">
-        <v>22</v>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>146276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46202</v>
       </c>
@@ -690,32 +662,29 @@
       <c r="F4">
         <v>12.09</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
+      <c r="G4" s="1">
+        <v>1.47</v>
       </c>
       <c r="H4">
-        <v>1.47</v>
+        <v>17.77</v>
       </c>
       <c r="I4" s="1">
-        <v>17.77</v>
+        <v>1.5</v>
       </c>
       <c r="J4">
-        <v>1.5</v>
-      </c>
-      <c r="K4" s="1">
         <v>18.13</v>
       </c>
-      <c r="L4" t="s">
-        <v>23</v>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>146277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46202</v>
       </c>
@@ -734,34 +703,31 @@
       <c r="F5">
         <v>31.39</v>
       </c>
-      <c r="G5" t="s">
-        <v>20</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>20.4</v>
       </c>
       <c r="I5" s="1">
-        <v>20.4</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>20.72</v>
       </c>
-      <c r="L5" t="s">
-        <v>24</v>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>62182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -769,27 +735,27 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -809,7 +775,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -829,9 +795,9 @@
         <v>18.13</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B12" s="10">
         <v>85.37</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,10 +55,16 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Бургас</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
   </si>
   <si>
     <t>В8986ВР</t>
@@ -64,22 +73,49 @@
     <t>78970155027720873</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>2026-07-02 06:53:39</t>
-  </si>
-  <si>
-    <t>2026-07-02 06:54:02</t>
-  </si>
-  <si>
-    <t>2026-07-09 11:08:18</t>
-  </si>
-  <si>
-    <t>2026-07-13 13:34:45</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:51:00</t>
+  </si>
+  <si>
+    <t>06:53:00</t>
+  </si>
+  <si>
+    <t>10:07:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>11:17:00</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
+    <t>3234860477 3234860477</t>
+  </si>
+  <si>
+    <t>3234860478 3234860478</t>
+  </si>
+  <si>
+    <t>3234889862 3234889862</t>
+  </si>
+  <si>
+    <t>3234937400 3234937400</t>
+  </si>
+  <si>
+    <t>3235415001 3235415001</t>
+  </si>
+  <si>
+    <t>3235415003 3235415003</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -499,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,15 +544,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -553,250 +591,368 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46205</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>4.4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.47</v>
+      </c>
+      <c r="I2" s="1">
+        <v>6.47</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>21.54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>0.62</v>
+      </c>
+      <c r="I3" s="1">
+        <v>13.35</v>
+      </c>
+      <c r="J3">
+        <v>0.63</v>
+      </c>
+      <c r="K3" s="1">
+        <v>13.57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>19.59</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>0.62</v>
+      </c>
+      <c r="I4" s="1">
+        <v>12.15</v>
+      </c>
+      <c r="J4">
+        <v>0.63</v>
+      </c>
+      <c r="K4" s="1">
+        <v>12.34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>32.92</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>28.8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5">
+        <v>0.65</v>
+      </c>
+      <c r="I5" s="1">
+        <v>18.72</v>
+      </c>
+      <c r="J5">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>19.01</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>6.71</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6">
+        <v>1.53</v>
+      </c>
+      <c r="I6" s="1">
+        <v>10.27</v>
+      </c>
+      <c r="J6">
+        <v>1.56</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10.47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>32.16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>0.63</v>
+      </c>
+      <c r="I7" s="1">
+        <v>20.26</v>
+      </c>
+      <c r="J7">
         <v>0.64</v>
       </c>
-      <c r="H2">
-        <v>21.07</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>21.4</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
+      <c r="K7" s="1">
+        <v>20.58</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46205</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>7.47</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H3">
-        <v>10.98</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J3">
-        <v>11.2</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7">
+        <v>102.09</v>
+      </c>
+      <c r="C12" s="7">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>64.48</v>
+      </c>
+      <c r="F12" s="7">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46212</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>32.57</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H4">
-        <v>20.19</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J4">
-        <v>20.52</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>20.42</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="H5">
-        <v>12.86</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="J5">
-        <v>13.07</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="7">
-        <v>85.91</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E10" s="7">
-        <v>54.12</v>
-      </c>
-      <c r="F10" s="7">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="7">
-        <v>7.47</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.4699</v>
-      </c>
-      <c r="E11" s="7">
-        <v>10.98</v>
-      </c>
-      <c r="F11" s="7">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="10">
-        <v>93.38</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="F12" s="10">
-        <v>66.19</v>
+      <c r="B13" s="7">
+        <v>11.11</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.5068</v>
+      </c>
+      <c r="E13" s="7">
+        <v>16.74</v>
+      </c>
+      <c r="F13" s="7">
+        <v>17.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="10">
+        <v>113.2</v>
+      </c>
+      <c r="C14" s="10">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10">
+        <v>81.22</v>
+      </c>
+      <c r="F14" s="10">
+        <v>82.56999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -143,7 +143,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -923,7 +923,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="8">
-        <v>1.5068</v>
+        <v>1.506751</v>
       </c>
       <c r="E13" s="7">
         <v>16.74</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,13 +551,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,274 +600,295 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>4.4</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
+        <v>1.369</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.47</v>
       </c>
-      <c r="I2" s="1">
-        <v>6.47</v>
-      </c>
       <c r="J2">
+        <v>6.468</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>6.6</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>21.54</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.62</v>
       </c>
-      <c r="I3" s="1">
-        <v>13.35</v>
-      </c>
       <c r="J3">
+        <v>13.3548</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.63</v>
       </c>
-      <c r="K3" s="1">
-        <v>13.57</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>13.5702</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>19.59</v>
+        <v>19.587</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.62</v>
       </c>
-      <c r="I4" s="1">
-        <v>12.15</v>
-      </c>
       <c r="J4">
+        <v>12.14394</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.63</v>
       </c>
-      <c r="K4" s="1">
-        <v>12.34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>12.33981</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>28.8</v>
+        <v>28.803</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>0.65</v>
       </c>
-      <c r="I5" s="1">
-        <v>18.72</v>
-      </c>
       <c r="J5">
+        <v>18.72195</v>
+      </c>
+      <c r="K5" s="1">
         <v>0.66</v>
       </c>
-      <c r="K5" s="1">
-        <v>19.01</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>19.00998</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46230</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>6.71</v>
+        <v>6.712</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6">
+        <v>1.401</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.53</v>
       </c>
-      <c r="I6" s="1">
-        <v>10.27</v>
-      </c>
       <c r="J6">
+        <v>10.26936</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.56</v>
       </c>
-      <c r="K6" s="1">
-        <v>10.47</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>10.47072</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46230</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>32.16</v>
+        <v>32.156</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>0.63</v>
       </c>
-      <c r="I7" s="1">
-        <v>20.26</v>
-      </c>
       <c r="J7">
+        <v>20.25828</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.64</v>
       </c>
-      <c r="K7" s="1">
-        <v>20.58</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>20.57984</v>
+      </c>
+      <c r="M7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -872,38 +896,38 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="7">
-        <v>102.09</v>
+        <v>102.086</v>
       </c>
       <c r="C12" s="7">
         <v>4</v>
       </c>
       <c r="D12" s="8">
-        <v>0.6316000000000001</v>
+        <v>0.631614</v>
       </c>
       <c r="E12" s="7">
         <v>64.48</v>
@@ -912,18 +936,18 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="7">
-        <v>11.11</v>
+        <v>11.112</v>
       </c>
       <c r="C13" s="7">
         <v>2</v>
       </c>
       <c r="D13" s="8">
-        <v>1.506751</v>
+        <v>1.506242</v>
       </c>
       <c r="E13" s="7">
         <v>16.74</v>
@@ -932,12 +956,12 @@
         <v>17.07</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="10">
-        <v>113.2</v>
+        <v>113.198</v>
       </c>
       <c r="C14" s="10">
         <v>6</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -144,9 +141,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -240,10 +237,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -551,13 +548,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -600,295 +597,274 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
       <c r="F2">
         <v>4.4</v>
       </c>
       <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.47</v>
+      </c>
+      <c r="I2" s="1">
+        <v>6.468</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="J2">
-        <v>6.468</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>21.54</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I3" s="1">
-        <v>0.62</v>
+        <v>13.355</v>
       </c>
       <c r="J3">
-        <v>13.3548</v>
+        <v>0.63</v>
       </c>
       <c r="K3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L3" s="1">
-        <v>13.5702</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3">
+        <v>13.57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>19.587</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I4" s="1">
-        <v>0.62</v>
+        <v>12.144</v>
       </c>
       <c r="J4">
-        <v>12.14394</v>
+        <v>0.63</v>
       </c>
       <c r="K4" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L4" s="1">
-        <v>12.33981</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4">
+        <v>12.34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>28.803</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>0.65</v>
+        <v>18.722</v>
       </c>
       <c r="J5">
-        <v>18.72195</v>
+        <v>0.66</v>
       </c>
       <c r="K5" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L5" s="1">
-        <v>19.00998</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5">
+        <v>19.01</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46230</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
       </c>
       <c r="F6">
         <v>6.712</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H6">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I6" s="1">
-        <v>1.53</v>
+        <v>10.269</v>
       </c>
       <c r="J6">
-        <v>10.26936</v>
+        <v>1.56</v>
       </c>
       <c r="K6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L6" s="1">
-        <v>10.47072</v>
-      </c>
-      <c r="M6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6">
+        <v>10.471</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46230</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>32.156</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="1">
-        <v>0.63</v>
+        <v>20.258</v>
       </c>
       <c r="J7">
-        <v>20.25828</v>
+        <v>0.64</v>
       </c>
       <c r="K7" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L7" s="1">
-        <v>20.57984</v>
-      </c>
-      <c r="M7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7">
+        <v>20.58</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -896,69 +872,69 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>102.086</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>4</v>
       </c>
       <c r="D12" s="8">
-        <v>0.631614</v>
-      </c>
-      <c r="E12" s="7">
-        <v>64.48</v>
-      </c>
-      <c r="F12" s="7">
+        <v>0.632</v>
+      </c>
+      <c r="E12" s="8">
+        <v>64.479</v>
+      </c>
+      <c r="F12" s="8">
         <v>65.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="7">
         <v>11.112</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>2</v>
       </c>
       <c r="D13" s="8">
-        <v>1.506242</v>
-      </c>
-      <c r="E13" s="7">
-        <v>16.74</v>
-      </c>
-      <c r="F13" s="7">
-        <v>17.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>1.506</v>
+      </c>
+      <c r="E13" s="8">
+        <v>16.737</v>
+      </c>
+      <c r="F13" s="8">
+        <v>17.071</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="10">
         <v>113.198</v>
@@ -968,10 +944,10 @@
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="10">
-        <v>81.22</v>
+        <v>81.21599999999999</v>
       </c>
       <c r="F14" s="10">
-        <v>82.56999999999999</v>
+        <v>82.571</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,13 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1925 HW Trakia, 243 km. Sofia direc</t>
-  </si>
-  <si>
-    <t>1195 243 Тракия Езеро</t>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В8986ВР</t>
@@ -73,49 +64,16 @@
     <t>78970155027720873</t>
   </si>
   <si>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>06:51:00</t>
-  </si>
-  <si>
-    <t>06:53:00</t>
-  </si>
-  <si>
-    <t>10:07:00</t>
-  </si>
-  <si>
-    <t>11:36:00</t>
-  </si>
-  <si>
-    <t>11:17:00</t>
-  </si>
-  <si>
-    <t>11:20:00</t>
-  </si>
-  <si>
-    <t>3234860477 3234860477</t>
-  </si>
-  <si>
-    <t>3234860478 3234860478</t>
-  </si>
-  <si>
-    <t>3234889862 3234889862</t>
-  </si>
-  <si>
-    <t>3234937400 3234937400</t>
-  </si>
-  <si>
-    <t>3235415001 3235415001</t>
-  </si>
-  <si>
-    <t>3235415003 3235415003</t>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>11:03</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -141,9 +99,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -237,10 +195,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -544,17 +502,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -594,365 +551,180 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>31.742</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>20.632</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>20.95</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>162861</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F3">
+        <v>11.929</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H3">
+        <v>18.132</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J3">
+        <v>18.49</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>4.4</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>162862</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.47</v>
-      </c>
-      <c r="I2" s="1">
-        <v>6.468</v>
-      </c>
-      <c r="J2">
-        <v>1.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7">
+        <v>31.742</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.64999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>20.63</v>
+      </c>
+      <c r="F8" s="7">
+        <v>20.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>21.54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>0.62</v>
-      </c>
-      <c r="I3" s="1">
-        <v>13.355</v>
-      </c>
-      <c r="J3">
-        <v>0.63</v>
-      </c>
-      <c r="K3" s="1">
-        <v>13.57</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
+      <c r="B9" s="7">
+        <v>11.929</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.51999</v>
+      </c>
+      <c r="E9" s="7">
+        <v>18.13</v>
+      </c>
+      <c r="F9" s="7">
+        <v>18.49</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>19.587</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>0.62</v>
-      </c>
-      <c r="I4" s="1">
-        <v>12.144</v>
-      </c>
-      <c r="J4">
-        <v>0.63</v>
-      </c>
-      <c r="K4" s="1">
-        <v>12.34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>28.803</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5">
-        <v>0.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>18.722</v>
-      </c>
-      <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
-        <v>19.01</v>
-      </c>
-      <c r="L5" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46230</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>6.712</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6">
-        <v>1.53</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10.269</v>
-      </c>
-      <c r="J6">
-        <v>1.56</v>
-      </c>
-      <c r="K6" s="1">
-        <v>10.471</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46230</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>32.156</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7">
-        <v>0.63</v>
-      </c>
-      <c r="I7" s="1">
-        <v>20.258</v>
-      </c>
-      <c r="J7">
-        <v>0.64</v>
-      </c>
-      <c r="K7" s="1">
-        <v>20.58</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="7">
-        <v>102.086</v>
-      </c>
-      <c r="C12" s="8">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.632</v>
-      </c>
-      <c r="E12" s="8">
-        <v>64.479</v>
-      </c>
-      <c r="F12" s="8">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="7">
-        <v>11.112</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B10" s="10">
+        <v>43.671</v>
+      </c>
+      <c r="C10" s="10">
         <v>2</v>
       </c>
-      <c r="D13" s="8">
-        <v>1.506</v>
-      </c>
-      <c r="E13" s="8">
-        <v>16.737</v>
-      </c>
-      <c r="F13" s="8">
-        <v>17.071</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="10">
-        <v>113.198</v>
-      </c>
-      <c r="C14" s="10">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>81.21599999999999</v>
-      </c>
-      <c r="F14" s="10">
-        <v>82.571</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>38.76</v>
+      </c>
+      <c r="F10" s="10">
+        <v>39.44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,7 +58,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1193 Казанлък</t>
   </si>
   <si>
     <t>В8986ВР</t>
@@ -67,13 +76,31 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>11:03</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:53:00</t>
+  </si>
+  <si>
+    <t>09:37:00</t>
+  </si>
+  <si>
+    <t>10:01:00</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>3236592608 3236592608</t>
+  </si>
+  <si>
+    <t>3236598375 3236598375</t>
+  </si>
+  <si>
+    <t>3236663062 3236663062</t>
+  </si>
+  <si>
+    <t>3236665115 3236665115</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -98,10 +125,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -181,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -195,10 +223,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -502,16 +532,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,180 +582,257 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>15.42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15.266</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10.177</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>11.61</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I3" s="1">
+        <v>11.494</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K3" s="1">
+        <v>7.663</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>31.742</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H2">
-        <v>20.632</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>17.23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17.058</v>
+      </c>
+      <c r="J4" s="1">
         <v>0.66</v>
       </c>
-      <c r="J2">
-        <v>20.95</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K4" s="1">
+        <v>11.372</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>15.7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15.543</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10.362</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>162861</v>
+      <c r="N5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>11.929</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>18.132</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>18.49</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>162862</v>
+      <c r="B10" s="7">
+        <v>59.96</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.9900099999999999</v>
+      </c>
+      <c r="E10" s="7">
+        <v>59.36</v>
+      </c>
+      <c r="F10" s="7">
+        <v>39.57</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7">
-        <v>31.742</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.64999</v>
-      </c>
-      <c r="E8" s="7">
-        <v>20.63</v>
-      </c>
-      <c r="F8" s="7">
-        <v>20.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7">
-        <v>11.929</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.51999</v>
-      </c>
-      <c r="E9" s="7">
-        <v>18.13</v>
-      </c>
-      <c r="F9" s="7">
-        <v>18.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="10">
-        <v>43.671</v>
-      </c>
-      <c r="C10" s="10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>38.76</v>
-      </c>
-      <c r="F10" s="10">
-        <v>39.44</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="11">
+        <v>59.96</v>
+      </c>
+      <c r="C11" s="12">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11">
+        <v>59.36</v>
+      </c>
+      <c r="F11" s="11">
+        <v>39.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -609,10 +609,10 @@
         <v>20</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>15.266</v>
+        <v>10.023</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -653,10 +653,10 @@
         <v>20</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>11.494</v>
+        <v>7.546</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -697,10 +697,10 @@
         <v>20</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>17.058</v>
+        <v>11.2</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -741,10 +741,10 @@
         <v>20</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>15.543</v>
+        <v>10.205</v>
       </c>
       <c r="J5" s="1">
         <v>0.66</v>
@@ -803,10 +803,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="9">
-        <v>0.9900099999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E10" s="7">
-        <v>59.36</v>
+        <v>38.97</v>
       </c>
       <c r="F10" s="7">
         <v>39.57</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="11">
-        <v>59.36</v>
+        <v>38.97</v>
       </c>
       <c r="F11" s="11">
         <v>39.57</v>
